--- a/data/trans_dic/IP16A01-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A01-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios</t>
+          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>96,02; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59,66; 85,89</t>
+          <t>58,0; 86,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,65; 74,36</t>
+          <t>40,34; 74,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50,34; 79,52</t>
+          <t>50,63; 80,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,66; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,9; 75,85</t>
+          <t>47,34; 75,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,65; 60,94</t>
+          <t>29,0; 63,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>48,38; 82,88</t>
+          <t>50,27; 84,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>97,89; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57,93; 77,42</t>
+          <t>57,31; 77,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39,69; 63,9</t>
+          <t>39,11; 64,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55,93; 78,26</t>
+          <t>55,83; 78,31</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>97,18; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47,41; 72,53</t>
+          <t>48,76; 72,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46,12; 70,01</t>
+          <t>45,16; 68,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,99; 66,52</t>
+          <t>32,08; 66,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>96,96; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,81; 68,44</t>
+          <t>42,37; 68,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,61; 75,74</t>
+          <t>50,72; 75,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>45,28; 66,9</t>
+          <t>45,38; 67,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>98,52; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48,06; 66,62</t>
+          <t>48,92; 66,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52,87; 69,41</t>
+          <t>52,64; 69,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>43,2; 63,37</t>
+          <t>43,32; 62,58</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>95,56; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50,54; 76,06</t>
+          <t>50,09; 75,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58,05; 83,33</t>
+          <t>58,01; 83,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,08; 83,48</t>
+          <t>28,78; 83,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>96,52; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55,9; 80,74</t>
+          <t>56,14; 80,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,77; 63,4</t>
+          <t>33,51; 65,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>41,96; 67,12</t>
+          <t>40,89; 67,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>98,02; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58,51; 75,51</t>
+          <t>57,68; 75,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50,25; 70,96</t>
+          <t>50,4; 70,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41,42; 74,75</t>
+          <t>41,58; 76,18</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>94,55; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>57,93; 81,32</t>
+          <t>57,7; 81,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42,81; 71,87</t>
+          <t>42,62; 72,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52,78; 80,3</t>
+          <t>52,82; 80,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,64; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,98; 72,79</t>
+          <t>47,88; 73,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,22; 70,98</t>
+          <t>41,75; 72,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,25; 74,39</t>
+          <t>45,23; 74,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>97,89; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57,62; 74,55</t>
+          <t>56,72; 73,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47,57; 68,22</t>
+          <t>47,67; 68,13</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53,22; 73,48</t>
+          <t>53,19; 73,54</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>99,0; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60,7; 73,37</t>
+          <t>60,42; 72,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53,45; 68,0</t>
+          <t>54,28; 68,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48,7; 76,03</t>
+          <t>47,96; 74,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>99,11; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,88; 68,32</t>
+          <t>56,39; 68,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,55; 62,83</t>
+          <t>47,95; 62,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>53,0; 66,52</t>
+          <t>51,99; 65,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>99,53; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60,41; 69,13</t>
+          <t>60,25; 69,2</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53,08; 63,13</t>
+          <t>53,5; 63,19</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>52,86; 68,42</t>
+          <t>52,52; 67,87</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>32818</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23486</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14378</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16952</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>21552</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>10580</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>19243</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>61492</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>45038</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>24958</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>36196</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18240; 27071</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9827; 18175</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13083; 20899</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>16295; 26035</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7012; 15288</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>13904; 23238</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>37753; 51306</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>18984; 31126</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>29871; 41895</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>41647</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24589</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24782</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>22722</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>22472</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>26510</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>36267</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>82952</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>47061</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>51293</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>58989</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>19798; 29474</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19284; 29315</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>14195; 29559</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>17083; 27552</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>20870; 30909</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>28954; 43134</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>39585; 53572</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>44138; 57943</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>46809; 67621</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>25164</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>21072</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19908</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>43507</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>25664</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>13642</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>31455</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>60286</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>46736</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>33550</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>74962</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16513; 25042</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16019; 23168</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>22178; 64689</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>20547; 29447</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>9318; 18084</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>23277; 38472</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>40129; 52447</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>27935; 38899</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>55710; 102078</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>25677</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29539</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19144</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>20837</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>29259</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>17246</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>20596</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>64494</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>58798</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>36391</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>41433</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>24112; 33892</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>13973; 23724</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>16142; 24653</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>22612; 34701</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>12587; 21921</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>15291; 25204</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>50491; 65862</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>29999; 42875</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>34236; 47339</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>125305</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>98686</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>78212</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>104018</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98947</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>67979</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>107562</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>269224</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>197633</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>146191</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>211579</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>88690; 107012</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>69181; 87247</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>85233; 133075</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>89414; 109213</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>59106; 77262</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>94726; 119965</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>183996; 211302</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>134154; 158441</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>189045; 244269</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A01-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A01-Habitat-trans_dic.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,0; 86,09</t>
+          <t>61,27; 86,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,34; 74,61</t>
+          <t>41,67; 75,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50,63; 80,87</t>
+          <t>49,26; 78,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,17 +742,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,34; 75,63</t>
+          <t>47,67; 75,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,0; 63,24</t>
+          <t>26,55; 62,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>50,27; 84,01</t>
+          <t>50,45; 82,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57,31; 77,89</t>
+          <t>58,4; 77,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39,11; 64,13</t>
+          <t>39,48; 64,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55,83; 78,31</t>
+          <t>55,65; 78,32</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,76; 72,59</t>
+          <t>47,82; 71,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,16; 68,65</t>
+          <t>46,85; 70,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,08; 66,81</t>
+          <t>31,29; 66,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,37; 68,33</t>
+          <t>42,58; 69,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,72; 75,12</t>
+          <t>51,99; 75,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>45,38; 67,6</t>
+          <t>46,43; 68,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48,92; 66,2</t>
+          <t>48,97; 66,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52,64; 69,11</t>
+          <t>51,25; 69,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>43,32; 62,58</t>
+          <t>44,45; 63,34</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50,09; 75,97</t>
+          <t>49,1; 75,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58,01; 83,9</t>
+          <t>57,28; 83,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28,78; 83,93</t>
+          <t>29,07; 86,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56,14; 80,45</t>
+          <t>55,85; 80,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,51; 65,04</t>
+          <t>32,89; 64,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40,89; 67,59</t>
+          <t>40,18; 67,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57,68; 75,39</t>
+          <t>58,12; 75,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50,4; 70,19</t>
+          <t>49,56; 69,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41,58; 76,18</t>
+          <t>41,5; 77,79</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1142,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>57,7; 81,11</t>
+          <t>58,16; 82,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42,62; 72,36</t>
+          <t>43,69; 72,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52,82; 80,67</t>
+          <t>54,28; 80,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,17 +1162,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,88; 73,47</t>
+          <t>49,78; 73,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,75; 72,72</t>
+          <t>43,07; 71,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45,23; 74,55</t>
+          <t>47,07; 75,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56,72; 73,99</t>
+          <t>57,41; 73,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47,67; 68,13</t>
+          <t>47,33; 67,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53,19; 73,54</t>
+          <t>54,02; 74,06</t>
         </is>
       </c>
     </row>
@@ -1282,17 +1282,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60,42; 72,9</t>
+          <t>61,17; 73,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54,28; 68,45</t>
+          <t>53,74; 68,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47,96; 74,88</t>
+          <t>48,28; 74,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,39; 68,87</t>
+          <t>56,07; 69,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,95; 62,67</t>
+          <t>47,78; 62,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>51,99; 65,84</t>
+          <t>52,18; 65,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60,25; 69,2</t>
+          <t>59,66; 69,02</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53,5; 63,19</t>
+          <t>52,85; 62,89</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>52,52; 67,87</t>
+          <t>53,2; 67,73</t>
         </is>
       </c>
     </row>
@@ -1650,17 +1650,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18240; 27071</t>
+          <t>19266; 27148</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9827; 18175</t>
+          <t>10149; 18417</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13083; 20899</t>
+          <t>12728; 20323</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1670,17 +1670,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16295; 26035</t>
+          <t>16411; 25973</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7012; 15288</t>
+          <t>6419; 14999</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13904; 23238</t>
+          <t>13954; 22936</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1690,17 +1690,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37753; 51306</t>
+          <t>38470; 50845</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18984; 31126</t>
+          <t>19162; 31178</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29871; 41895</t>
+          <t>29773; 41900</t>
         </is>
       </c>
     </row>
@@ -1858,17 +1858,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19798; 29474</t>
+          <t>19417; 29208</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19284; 29315</t>
+          <t>20005; 29939</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14195; 29559</t>
+          <t>13842; 29459</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1878,17 +1878,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17083; 27552</t>
+          <t>17168; 27827</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20870; 30909</t>
+          <t>21391; 30984</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28954; 43134</t>
+          <t>29624; 43441</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39585; 53572</t>
+          <t>39623; 53491</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44138; 57943</t>
+          <t>42971; 57936</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46809; 67621</t>
+          <t>48031; 68435</t>
         </is>
       </c>
     </row>
@@ -2066,17 +2066,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16513; 25042</t>
+          <t>16184; 24847</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16019; 23168</t>
+          <t>15818; 23155</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22178; 64689</t>
+          <t>22408; 66646</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2086,17 +2086,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20547; 29447</t>
+          <t>20443; 29384</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9318; 18084</t>
+          <t>9145; 17868</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23277; 38472</t>
+          <t>22869; 38203</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2106,17 +2106,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40129; 52447</t>
+          <t>40430; 52481</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27935; 38899</t>
+          <t>27466; 38738</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>55710; 102078</t>
+          <t>55613; 104233</t>
         </is>
       </c>
     </row>
@@ -2274,17 +2274,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24112; 33892</t>
+          <t>24302; 34546</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13973; 23724</t>
+          <t>14325; 23908</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16142; 24653</t>
+          <t>16587; 24510</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2294,17 +2294,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22612; 34701</t>
+          <t>23508; 34665</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12587; 21921</t>
+          <t>12984; 21569</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15291; 25204</t>
+          <t>15913; 25585</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2314,17 +2314,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50491; 65862</t>
+          <t>51100; 65811</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29999; 42875</t>
+          <t>29786; 42578</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>34236; 47339</t>
+          <t>34770; 47673</t>
         </is>
       </c>
     </row>
@@ -2482,17 +2482,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>88690; 107012</t>
+          <t>89801; 108483</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>69181; 87247</t>
+          <t>68501; 86885</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85233; 133075</t>
+          <t>85806; 131950</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89414; 109213</t>
+          <t>88910; 109578</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>59106; 77262</t>
+          <t>58903; 76857</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>94726; 119965</t>
+          <t>95069; 120047</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2522,17 +2522,17 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>183996; 211302</t>
+          <t>182190; 210777</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>134154; 158441</t>
+          <t>132523; 157678</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>189045; 244269</t>
+          <t>191488; 243782</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A01-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A01-Habitat-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
+          <t>Menores que consumieron medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -654,44 +654,44 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>62,61%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>43,76%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>71,99%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>74,69%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>59,02%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>65,6%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>66,28%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>62,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>43,76%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>69,57%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>68,37%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>69,04%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>61,27; 86,33</t>
+          <t>47,9; 75,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41,67; 75,6</t>
+          <t>25,65; 60,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49,26; 78,65</t>
+          <t>50,71; 84,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,17 +742,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,67; 75,45</t>
+          <t>59,66; 85,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,55; 62,04</t>
+          <t>39,65; 74,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>50,45; 82,92</t>
+          <t>50,6; 80,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58,4; 77,19</t>
+          <t>57,93; 77,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39,48; 64,24</t>
+          <t>39,69; 63,9</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55,65; 78,32</t>
+          <t>57,47; 78,95</t>
         </is>
       </c>
     </row>
@@ -794,44 +794,44 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>55,73%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64,43%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>57,99%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>60,56%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>58,04%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>51,36%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>58,64%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>55,73%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>64,43%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>56,84%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>58,16%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>58,24%</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47,82; 71,94</t>
+          <t>41,81; 68,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46,85; 70,12</t>
+          <t>51,61; 75,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,29; 66,59</t>
+          <t>46,46; 68,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,58; 69,01</t>
+          <t>47,41; 72,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,99; 75,3</t>
+          <t>46,12; 70,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,43; 68,08</t>
+          <t>45,69; 70,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48,97; 66,1</t>
+          <t>48,06; 66,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51,25; 69,1</t>
+          <t>52,87; 69,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>44,45; 63,34</t>
+          <t>50,11; 67,07</t>
         </is>
       </c>
     </row>
@@ -934,44 +934,44 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>70,12%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>49,06%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>55,53%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>63,93%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>72,09%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>56,45%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>38,55%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>49,06%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>55,26%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>67,18%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>47,17%</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>49,1; 75,38</t>
+          <t>55,9; 80,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,28; 83,85</t>
+          <t>32,77; 63,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,07; 86,47</t>
+          <t>40,81; 67,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55,85; 80,28</t>
+          <t>50,54; 76,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,89; 64,26</t>
+          <t>58,05; 83,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40,18; 67,11</t>
+          <t>26,87; 53,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58,12; 75,44</t>
+          <t>58,51; 75,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49,56; 69,9</t>
+          <t>50,25; 70,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41,5; 77,79</t>
+          <t>38,22; 57,41</t>
         </is>
       </c>
     </row>
@@ -1074,44 +1074,44 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>61,95%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>57,21%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>59,09%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>70,69%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>58,39%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>68,18%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>66,47%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>61,95%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>57,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>60,92%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>66,05%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>62,67%</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1142,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>58,16; 82,67</t>
+          <t>48,98; 72,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43,69; 72,92</t>
+          <t>40,22; 70,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54,28; 80,2</t>
+          <t>44,06; 73,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,17 +1162,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,78; 73,4</t>
+          <t>57,93; 81,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,07; 71,55</t>
+          <t>42,81; 71,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47,07; 75,67</t>
+          <t>51,19; 79,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57,41; 73,93</t>
+          <t>57,62; 74,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47,33; 67,65</t>
+          <t>47,57; 68,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54,02; 74,06</t>
+          <t>51,51; 72,15</t>
         </is>
       </c>
     </row>
@@ -1214,44 +1214,44 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>62,4%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55,14%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>59,51%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>67,23%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>61,36%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>58,53%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>54,53%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>62,4%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>55,14%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>59,03%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>64,72%</t>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>57,2%</t>
         </is>
       </c>
     </row>
@@ -1282,17 +1282,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>61,17; 73,9</t>
+          <t>55,88; 68,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53,74; 68,17</t>
+          <t>47,55; 62,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48,28; 74,25</t>
+          <t>53,33; 66,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,07; 69,1</t>
+          <t>60,7; 73,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,78; 62,35</t>
+          <t>53,45; 68,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>52,18; 65,89</t>
+          <t>47,2; 61,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59,66; 69,02</t>
+          <t>60,41; 69,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52,85; 62,89</t>
+          <t>53,08; 63,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>53,2; 67,73</t>
+          <t>52,4; 61,93</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
+          <t>Menores que consumieron medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,37 +1509,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21552</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10580</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17726</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>23486</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>14378</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16952</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>21552</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10580</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19243</t>
+          <t>17437</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36196</t>
+          <t>35163</t>
         </is>
       </c>
     </row>
@@ -1650,17 +1650,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19266; 27148</t>
+          <t>16488; 26111</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10149; 18417</t>
+          <t>6202; 14732</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12728; 20323</t>
+          <t>12485; 20925</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1670,17 +1670,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16411; 25973</t>
+          <t>18760; 27009</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6419; 14999</t>
+          <t>9657; 18113</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13954; 22936</t>
+          <t>13312; 21131</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1690,17 +1690,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38470; 50845</t>
+          <t>38159; 50995</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19162; 31178</t>
+          <t>19265; 31016</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29773; 41900</t>
+          <t>29267; 40210</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>22472</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>26510</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>32741</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>24589</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>24782</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22722</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>22472</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>26510</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36267</t>
+          <t>21190</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58989</t>
+          <t>53931</t>
         </is>
       </c>
     </row>
@@ -1858,17 +1858,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19417; 29208</t>
+          <t>16857; 27594</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20005; 29939</t>
+          <t>21238; 31163</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13842; 29459</t>
+          <t>26228; 38632</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1878,17 +1878,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17168; 27827</t>
+          <t>19251; 29447</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21391; 30984</t>
+          <t>19692; 29893</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29624; 43441</t>
+          <t>16510; 25621</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39623; 53491</t>
+          <t>38889; 53910</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42971; 57936</t>
+          <t>44328; 58201</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48031; 68435</t>
+          <t>46402; 62107</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>25664</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>13642</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>29072</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>21072</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>19908</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>43507</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>25664</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>13642</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31455</t>
+          <t>19595</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74962</t>
+          <t>48667</t>
         </is>
       </c>
     </row>
@@ -2066,17 +2066,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16184; 24847</t>
+          <t>20458; 29550</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15818; 23155</t>
+          <t>9111; 17628</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22408; 66646</t>
+          <t>21367; 35231</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2086,17 +2086,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20443; 29384</t>
+          <t>16659; 25073</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9145; 17868</t>
+          <t>16031; 23011</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22869; 38203</t>
+          <t>13657; 27306</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2106,17 +2106,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40430; 52481</t>
+          <t>40700; 52527</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27466; 38738</t>
+          <t>27849; 39327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>55613; 104233</t>
+          <t>39435; 59233</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29259</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>17246</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>18623</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>29539</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>19144</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20837</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>29259</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17246</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>19756</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41433</t>
+          <t>38378</t>
         </is>
       </c>
     </row>
@@ -2274,17 +2274,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24302; 34546</t>
+          <t>23134; 34379</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14325; 23908</t>
+          <t>12125; 21399</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16587; 24510</t>
+          <t>13886; 23070</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2294,17 +2294,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23508; 34665</t>
+          <t>24206; 33982</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12984; 21569</t>
+          <t>14035; 23566</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15913; 25585</t>
+          <t>15217; 23485</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2314,17 +2314,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51100; 65811</t>
+          <t>51293; 66359</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29786; 42578</t>
+          <t>29941; 42932</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>34770; 47673</t>
+          <t>31545; 44186</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>119</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>125</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>98947</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>67979</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>98162</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>98686</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>78212</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>104018</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98947</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>67979</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>107562</t>
+          <t>77978</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>211579</t>
+          <t>176140</t>
         </is>
       </c>
     </row>
@@ -2482,17 +2482,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>89801; 108483</t>
+          <t>88618; 108340</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>68501; 86885</t>
+          <t>58624; 77455</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85806; 131950</t>
+          <t>87974; 110339</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88910; 109578</t>
+          <t>89108; 107709</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>58903; 76857</t>
+          <t>68124; 86669</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>95069; 120047</t>
+          <t>67490; 87349</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2522,17 +2522,17 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182190; 210777</t>
+          <t>184488; 211108</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>132523; 157678</t>
+          <t>133087; 158295</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>191488; 243782</t>
+          <t>161358; 190697</t>
         </is>
       </c>
     </row>
